--- a/output.xlsx
+++ b/output.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="243" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="513" uniqueCount="26">
   <si>
     <t>AAPL</t>
   </si>
@@ -144,25 +144,25 @@
   <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.08984375" customWidth="true"/>
-    <col min="2" max="2" width="12.453125" customWidth="true"/>
-    <col min="3" max="3" width="13.08984375" customWidth="true"/>
-    <col min="4" max="4" width="13.08984375" customWidth="true"/>
-    <col min="5" max="5" width="12.08984375" customWidth="true"/>
-    <col min="6" max="6" width="14.08984375" customWidth="true"/>
-    <col min="7" max="7" width="13.08984375" customWidth="true"/>
-    <col min="8" max="8" width="14.08984375" customWidth="true"/>
-    <col min="9" max="9" width="12.453125" customWidth="true"/>
-    <col min="10" max="10" width="13.08984375" customWidth="true"/>
-    <col min="11" max="11" width="13.08984375" customWidth="true"/>
-    <col min="12" max="12" width="12.08984375" customWidth="true"/>
-    <col min="13" max="13" width="13.08984375" customWidth="true"/>
-    <col min="14" max="14" width="13.453125" customWidth="true"/>
-    <col min="15" max="15" width="13.08984375" customWidth="true"/>
-    <col min="16" max="16" width="13.08984375" customWidth="true"/>
-    <col min="17" max="17" width="12.453125" customWidth="true"/>
-    <col min="18" max="18" width="14.453125" customWidth="true"/>
-    <col min="19" max="19" width="3.54296875" customWidth="true"/>
+    <col min="1" max="1" width="13.21875" customWidth="true"/>
+    <col min="2" max="2" width="12.5546875" customWidth="true"/>
+    <col min="3" max="3" width="13.21875" customWidth="true"/>
+    <col min="4" max="4" width="13.21875" customWidth="true"/>
+    <col min="5" max="5" width="12.21875" customWidth="true"/>
+    <col min="6" max="6" width="14.21875" customWidth="true"/>
+    <col min="7" max="7" width="13.21875" customWidth="true"/>
+    <col min="8" max="8" width="14.21875" customWidth="true"/>
+    <col min="9" max="9" width="12.5546875" customWidth="true"/>
+    <col min="10" max="10" width="13.21875" customWidth="true"/>
+    <col min="11" max="11" width="13.21875" customWidth="true"/>
+    <col min="12" max="12" width="12.21875" customWidth="true"/>
+    <col min="13" max="13" width="13.21875" customWidth="true"/>
+    <col min="14" max="14" width="13.5546875" customWidth="true"/>
+    <col min="15" max="15" width="13.21875" customWidth="true"/>
+    <col min="16" max="16" width="13.21875" customWidth="true"/>
+    <col min="17" max="17" width="12.5546875" customWidth="true"/>
+    <col min="18" max="18" width="14.5546875" customWidth="true"/>
+    <col min="19" max="19" width="3.6640625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -705,25 +705,25 @@
   <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.08984375" customWidth="true"/>
-    <col min="2" max="2" width="13.08984375" customWidth="true"/>
-    <col min="3" max="3" width="13.08984375" customWidth="true"/>
-    <col min="4" max="4" width="14.08984375" customWidth="true"/>
-    <col min="5" max="5" width="13.08984375" customWidth="true"/>
-    <col min="6" max="6" width="13.08984375" customWidth="true"/>
-    <col min="7" max="7" width="13.08984375" customWidth="true"/>
-    <col min="8" max="8" width="14.08984375" customWidth="true"/>
-    <col min="9" max="9" width="13.453125" customWidth="true"/>
-    <col min="10" max="10" width="13.08984375" customWidth="true"/>
-    <col min="11" max="11" width="13.08984375" customWidth="true"/>
-    <col min="12" max="12" width="12.453125" customWidth="true"/>
-    <col min="13" max="13" width="13.08984375" customWidth="true"/>
-    <col min="14" max="14" width="13.453125" customWidth="true"/>
-    <col min="15" max="15" width="13.08984375" customWidth="true"/>
-    <col min="16" max="16" width="13.453125" customWidth="true"/>
-    <col min="17" max="17" width="13.453125" customWidth="true"/>
-    <col min="18" max="18" width="15.453125" customWidth="true"/>
-    <col min="19" max="19" width="3.54296875" customWidth="true"/>
+    <col min="1" max="1" width="13.21875" customWidth="true"/>
+    <col min="2" max="2" width="13.21875" customWidth="true"/>
+    <col min="3" max="3" width="13.21875" customWidth="true"/>
+    <col min="4" max="4" width="13.21875" customWidth="true"/>
+    <col min="5" max="5" width="13.21875" customWidth="true"/>
+    <col min="6" max="6" width="14.21875" customWidth="true"/>
+    <col min="7" max="7" width="13.21875" customWidth="true"/>
+    <col min="8" max="8" width="13.21875" customWidth="true"/>
+    <col min="9" max="9" width="12.5546875" customWidth="true"/>
+    <col min="10" max="10" width="13.21875" customWidth="true"/>
+    <col min="11" max="11" width="13.21875" customWidth="true"/>
+    <col min="12" max="12" width="13.21875" customWidth="true"/>
+    <col min="13" max="13" width="14.21875" customWidth="true"/>
+    <col min="14" max="14" width="13.5546875" customWidth="true"/>
+    <col min="15" max="15" width="13.21875" customWidth="true"/>
+    <col min="16" max="16" width="13.21875" customWidth="true"/>
+    <col min="17" max="17" width="13.21875" customWidth="true"/>
+    <col min="18" max="18" width="14.5546875" customWidth="true"/>
+    <col min="19" max="19" width="3.6640625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -787,58 +787,58 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>-1.3575176488719649</v>
+        <v>-1.3670022696532742</v>
       </c>
       <c r="B2" s="0">
-        <v>2.090301048233532</v>
+        <v>0.54598044517441191</v>
       </c>
       <c r="C2" s="0">
-        <v>-0.54778627835990379</v>
+        <v>-1.5143992937942583</v>
       </c>
       <c r="D2" s="0">
-        <v>2.4991347888464075</v>
+        <v>2.2202707627660767</v>
       </c>
       <c r="E2" s="0">
-        <v>-2.6688373388585553</v>
+        <v>-1.703868320302206</v>
       </c>
       <c r="F2" s="0">
-        <v>-0.005468237599867279</v>
+        <v>-0.053078419990657877</v>
       </c>
       <c r="G2" s="0">
-        <v>-0.31987985697068544</v>
+        <v>-0.88130994641270466</v>
       </c>
       <c r="H2" s="0">
-        <v>-0.077488908940254508</v>
+        <v>-0.15219786277932543</v>
       </c>
       <c r="I2" s="0">
-        <v>0.27200301330875765</v>
+        <v>0.25790944667993471</v>
       </c>
       <c r="J2" s="0">
-        <v>-0.31230182463128847</v>
+        <v>-0.30493008695048024</v>
       </c>
       <c r="K2" s="0">
-        <v>0.14123268470783396</v>
+        <v>0.1535960163412631</v>
       </c>
       <c r="L2" s="0">
-        <v>-1.4459514954152355</v>
+        <v>-0.96043015940212739</v>
       </c>
       <c r="M2" s="0">
-        <v>1.1550933896281903</v>
+        <v>0.4204228270742521</v>
       </c>
       <c r="N2" s="0">
-        <v>-0.45775054886780259</v>
+        <v>-0.71690434905740552</v>
       </c>
       <c r="O2" s="0">
-        <v>0.26385471112842202</v>
+        <v>0.41414816170425217</v>
       </c>
       <c r="P2" s="0">
-        <v>-0.59333296561941529</v>
+        <v>-1.4759391347167092</v>
       </c>
       <c r="Q2" s="0">
-        <v>-1.2894715950908162</v>
+        <v>-0.46826578074244046</v>
       </c>
       <c r="R2" s="0">
-        <v>-1.8307635424830984</v>
+        <v>-1.2997696130098841</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>19</v>
@@ -846,58 +846,58 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>-0.050856625194873044</v>
+        <v>-0.14253613363470924</v>
       </c>
       <c r="B3" s="0">
-        <v>2.704599983320906</v>
+        <v>1.0021229202542201</v>
       </c>
       <c r="C3" s="0">
-        <v>0.76294951751023821</v>
+        <v>0.79556330220959293</v>
       </c>
       <c r="D3" s="0">
-        <v>1.0725207892908637</v>
+        <v>0.59352199024378338</v>
       </c>
       <c r="E3" s="0">
-        <v>12.31487948826069</v>
+        <v>1.88230710043976</v>
       </c>
       <c r="F3" s="0">
-        <v>0.50824522535684358</v>
+        <v>0.51091006207515211</v>
       </c>
       <c r="G3" s="0">
-        <v>0.67925674932386493</v>
+        <v>1.9950055046325064</v>
       </c>
       <c r="H3" s="0">
-        <v>0.1618988957169907</v>
+        <v>0.30332275109744489</v>
       </c>
       <c r="I3" s="0">
-        <v>0.056938156742664309</v>
+        <v>0.30259437090509828</v>
       </c>
       <c r="J3" s="0">
-        <v>-0.22599282213774086</v>
+        <v>-0.61414947818872279</v>
       </c>
       <c r="K3" s="0">
-        <v>-0.21380238564578727</v>
+        <v>-0.32984278475618545</v>
       </c>
       <c r="L3" s="0">
-        <v>-1.9637633152403677</v>
+        <v>-0.49198390722168434</v>
       </c>
       <c r="M3" s="0">
-        <v>2.7313028772088774</v>
+        <v>0.61923270725073698</v>
       </c>
       <c r="N3" s="0">
-        <v>-1.1246336696116568</v>
+        <v>-0.42168661280366171</v>
       </c>
       <c r="O3" s="0">
-        <v>-4.3873042595059122</v>
+        <v>-0.7131636148076953</v>
       </c>
       <c r="P3" s="0">
-        <v>-0.10284278475270278</v>
+        <v>-0.27271696506662102</v>
       </c>
       <c r="Q3" s="0">
-        <v>-1.6905930590190672</v>
+        <v>-0.58561449240039443</v>
       </c>
       <c r="R3" s="0">
-        <v>0.64153004092727228</v>
+        <v>2.5527896394777296</v>
       </c>
       <c r="S3" s="0" t="s">
         <v>20</v>
@@ -905,58 +905,58 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>-0.71089207099317242</v>
+        <v>-0.64439378307065021</v>
       </c>
       <c r="B4" s="0">
-        <v>0.81508058377344539</v>
+        <v>0.1957481675972573</v>
       </c>
       <c r="C4" s="0">
-        <v>0.11044307735924222</v>
+        <v>0.12335085013351628</v>
       </c>
       <c r="D4" s="0">
-        <v>-0.7632279237830224</v>
+        <v>-0.64515488746139171</v>
       </c>
       <c r="E4" s="0">
-        <v>-0.44709924956836194</v>
+        <v>-0.202680081094959</v>
       </c>
       <c r="F4" s="0">
-        <v>0.18660782889459421</v>
+        <v>0.25075829935224958</v>
       </c>
       <c r="G4" s="0">
-        <v>0.042289736004996602</v>
+        <v>0.19500135612339772</v>
       </c>
       <c r="H4" s="0">
-        <v>-0.072945389354537885</v>
+        <v>-0.87235407150441713</v>
       </c>
       <c r="I4" s="0">
-        <v>0.17234844944611433</v>
+        <v>0.51197547420201017</v>
       </c>
       <c r="J4" s="0">
-        <v>-0.96596201996257714</v>
+        <v>-0.84900398235989383</v>
       </c>
       <c r="K4" s="0">
-        <v>0.46875165612188585</v>
+        <v>0.46872321072935635</v>
       </c>
       <c r="L4" s="0">
-        <v>0.95224053860871261</v>
+        <v>0.25532626206801906</v>
       </c>
       <c r="M4" s="0">
-        <v>-1.1855408733277677</v>
+        <v>-0.41056242677452054</v>
       </c>
       <c r="N4" s="0">
-        <v>0.023491001674159861</v>
+        <v>0.026123242527119072</v>
       </c>
       <c r="O4" s="0">
-        <v>4.7946381598646335</v>
+        <v>1.041841297901188</v>
       </c>
       <c r="P4" s="0">
-        <v>0.030054283548675342</v>
+        <v>0.12512302299321906</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.050685389429251021</v>
+        <v>0.11206999891192794</v>
       </c>
       <c r="R4" s="0">
-        <v>0.028619095978136711</v>
+        <v>0.063655843470630053</v>
       </c>
       <c r="S4" s="0" t="s">
         <v>18</v>
@@ -964,58 +964,58 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>-2.7401192772915297</v>
+        <v>-2.3692409555440568</v>
       </c>
       <c r="B5" s="0">
-        <v>3.9831344581043213</v>
+        <v>5.3614965534566039</v>
       </c>
       <c r="C5" s="0">
-        <v>0.86973977199501662</v>
+        <v>2.7036263073726445</v>
       </c>
       <c r="D5" s="0">
-        <v>1.2808976544106614</v>
+        <v>1.5359386715258612</v>
       </c>
       <c r="E5" s="0">
-        <v>3.6173754968123082</v>
+        <v>0.61851524835028715</v>
       </c>
       <c r="F5" s="0">
-        <v>1.8188509481386115</v>
+        <v>1.5224302402857941</v>
       </c>
       <c r="G5" s="0">
-        <v>2.1407529094389863</v>
+        <v>2.3632822417573167</v>
       </c>
       <c r="H5" s="0">
-        <v>-1.9644063408736787</v>
+        <v>-2.4329143037818679</v>
       </c>
       <c r="I5" s="0">
-        <v>0.90824549503310248</v>
+        <v>2.8761622794796398</v>
       </c>
       <c r="J5" s="0">
-        <v>0.70567655240704974</v>
+        <v>0.59162627786381672</v>
       </c>
       <c r="K5" s="0">
-        <v>0.17287986025236093</v>
+        <v>0.9689066891144742</v>
       </c>
       <c r="L5" s="0">
-        <v>2.6425799326398787</v>
+        <v>1.9721077482608542</v>
       </c>
       <c r="M5" s="0">
-        <v>-2.7842283990592538</v>
+        <v>-1.3677831003111589</v>
       </c>
       <c r="N5" s="0">
-        <v>3.6237485167973684</v>
+        <v>1.5199639482352694</v>
       </c>
       <c r="O5" s="0">
-        <v>26.478039665954771</v>
+        <v>3.5838216999273489</v>
       </c>
       <c r="P5" s="0">
-        <v>1.0479595105456818</v>
+        <v>1.0445319855655475</v>
       </c>
       <c r="Q5" s="0">
-        <v>9.7034096374137473</v>
+        <v>2.2219356891035131</v>
       </c>
       <c r="R5" s="0">
-        <v>0.41261440741128291</v>
+        <v>0.97835194298303185</v>
       </c>
       <c r="S5" s="0" t="s">
         <v>21</v>
@@ -1023,58 +1023,58 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.14825607617045755</v>
+        <v>0.81825018249794646</v>
       </c>
       <c r="B6" s="0">
-        <v>-0.51448048215259023</v>
+        <v>-0.38709209543580908</v>
       </c>
       <c r="C6" s="0">
-        <v>-0.87432619536741696</v>
+        <v>-0.87902465919739425</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.84478633190212482</v>
+        <v>-0.65657679034851624</v>
       </c>
       <c r="E6" s="0">
-        <v>-19.246773113179671</v>
+        <v>-3.530036673063397</v>
       </c>
       <c r="F6" s="0">
-        <v>-1.3837541053370515</v>
+        <v>-1.7692037797582363</v>
       </c>
       <c r="G6" s="0">
-        <v>-0.15130092136874385</v>
+        <v>-0.49537882147501489</v>
       </c>
       <c r="H6" s="0">
-        <v>0.82855139039009873</v>
+        <v>1.3717319115640079</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.23171496527212035</v>
+        <v>-1.1520112999385874</v>
       </c>
       <c r="J6" s="0">
-        <v>0.20418654749687995</v>
+        <v>1.0927045209631066</v>
       </c>
       <c r="K6" s="0">
-        <v>-0.11356345163024405</v>
+        <v>-0.35576274763972632</v>
       </c>
       <c r="L6" s="0">
-        <v>-1.5722747085923357</v>
+        <v>-0.37949072846732235</v>
       </c>
       <c r="M6" s="0">
-        <v>-0.30875432901303729</v>
+        <v>-0.098311570355364628</v>
       </c>
       <c r="N6" s="0">
-        <v>0.098373235674342946</v>
+        <v>0.044229344710848238</v>
       </c>
       <c r="O6" s="0">
-        <v>-0.4960269667467096</v>
+        <v>-0.10255208612351963</v>
       </c>
       <c r="P6" s="0">
-        <v>-0.54715162283142005</v>
+        <v>-1.6174532837152746</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.94738626283396987</v>
+        <v>0.28999366397877885</v>
       </c>
       <c r="R6" s="0">
-        <v>0.0009456089251271187</v>
+        <v>0.0035200984324990367</v>
       </c>
       <c r="S6" s="0" t="s">
         <v>22</v>
@@ -1082,58 +1082,58 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>-1.1018563523791589</v>
+        <v>-0.6297948830402138</v>
       </c>
       <c r="B7" s="0">
-        <v>1.6062423844725489</v>
+        <v>1.2883232323044076</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.47883630077158229</v>
+        <v>-0.45920512564154475</v>
       </c>
       <c r="D7" s="0">
-        <v>0.023254922278206996</v>
+        <v>0.10130186639013491</v>
       </c>
       <c r="E7" s="0">
-        <v>3.8185207651587354</v>
+        <v>1.9492616243125924</v>
       </c>
       <c r="F7" s="0">
-        <v>2.3366275109458954</v>
+        <v>4.2379724210259564</v>
       </c>
       <c r="G7" s="0">
-        <v>0.33642076467080884</v>
+        <v>0.4154591673836826</v>
       </c>
       <c r="H7" s="0">
-        <v>-1.5139353110478686</v>
+        <v>-1.5612481814529402</v>
       </c>
       <c r="I7" s="0">
-        <v>0.8323699225815423</v>
+        <v>0.99075306678289343</v>
       </c>
       <c r="J7" s="0">
-        <v>-2.2630522409610268</v>
+        <v>-1.2542113663506511</v>
       </c>
       <c r="K7" s="0">
-        <v>0.63464158845355201</v>
+        <v>2.1194285120237257</v>
       </c>
       <c r="L7" s="0">
-        <v>-0.86649692504812215</v>
+        <v>-0.19949492825225343</v>
       </c>
       <c r="M7" s="0">
-        <v>-0.44489136540735658</v>
+        <v>-0.79397981417888264</v>
       </c>
       <c r="N7" s="0">
-        <v>0.17040603944283517</v>
+        <v>0.21324173974371521</v>
       </c>
       <c r="O7" s="0">
-        <v>1.9627585875735041</v>
+        <v>0.57564641192796107</v>
       </c>
       <c r="P7" s="0">
-        <v>1.8850001255878566</v>
+        <v>2.1017697044161228</v>
       </c>
       <c r="Q7" s="0">
-        <v>10.838986727425056</v>
+        <v>2.0666405467419526</v>
       </c>
       <c r="R7" s="0">
-        <v>-0.07123552013670606</v>
+        <v>-0.063487209111256632</v>
       </c>
       <c r="S7" s="0" t="s">
         <v>23</v>
@@ -1141,58 +1141,58 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>-1.4892827071319341</v>
+        <v>-1.1379039418060886</v>
       </c>
       <c r="B8" s="0">
-        <v>3.7811856522767293</v>
+        <v>4.7613957486458247</v>
       </c>
       <c r="C8" s="0">
-        <v>0.092279990996966932</v>
+        <v>0.56488630941782603</v>
       </c>
       <c r="D8" s="0">
-        <v>-0.045067563155289765</v>
+        <v>-0.10973646497766937</v>
       </c>
       <c r="E8" s="0">
-        <v>4.1154559726370046</v>
+        <v>0.67945886731810379</v>
       </c>
       <c r="F8" s="0">
-        <v>0.77893120071405309</v>
+        <v>0.91568677934285259</v>
       </c>
       <c r="G8" s="0">
-        <v>0.50967455563315356</v>
+        <v>0.69271226282762766</v>
       </c>
       <c r="H8" s="0">
-        <v>-0.73378016298970328</v>
+        <v>-1.1558706572314699</v>
       </c>
       <c r="I8" s="0">
-        <v>0.40257256579075346</v>
+        <v>1.4211503828690446</v>
       </c>
       <c r="J8" s="0">
-        <v>1.043659995303214</v>
+        <v>0.773195818696508</v>
       </c>
       <c r="K8" s="0">
-        <v>0.1360874662229091</v>
+        <v>0.71351136322551545</v>
       </c>
       <c r="L8" s="0">
-        <v>3.5705222054009607</v>
+        <v>5.247233824480567</v>
       </c>
       <c r="M8" s="0">
-        <v>-0.77113530298502486</v>
+        <v>-0.76925513762332343</v>
       </c>
       <c r="N8" s="0">
-        <v>10.395793042871713</v>
+        <v>4.2074125120322776</v>
       </c>
       <c r="O8" s="0">
-        <v>17.577344894066343</v>
+        <v>3.341345566901246</v>
       </c>
       <c r="P8" s="0">
-        <v>0.29561824316045893</v>
+        <v>0.3536997622815159</v>
       </c>
       <c r="Q8" s="0">
-        <v>8.550863567960219</v>
+        <v>2.4903757781420271</v>
       </c>
       <c r="R8" s="0">
-        <v>-0.15670241269822313</v>
+        <v>-0.41420194478897227</v>
       </c>
       <c r="S8" s="0" t="s">
         <v>24</v>
@@ -1200,58 +1200,58 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.12894556105508342</v>
+        <v>0.061369090445720025</v>
       </c>
       <c r="B9" s="0">
-        <v>-0.5509287769201624</v>
+        <v>-0.16609177535437819</v>
       </c>
       <c r="C9" s="0">
-        <v>-1.0858163409713875</v>
+        <v>-0.68835174528568266</v>
       </c>
       <c r="D9" s="0">
-        <v>-0.14818593118577878</v>
+        <v>-0.38464688604201691</v>
       </c>
       <c r="E9" s="0">
-        <v>-7.2988999785592288</v>
+        <v>-1.1494622552741831</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.21425032140546407</v>
+        <v>-1.4116701526313677</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.069824250220260398</v>
+        <v>-0.26413131252588506</v>
       </c>
       <c r="H9" s="0">
-        <v>0.68456123842913896</v>
+        <v>1.52969652833742</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.3559109372920784</v>
+        <v>-0.47390019236040093</v>
       </c>
       <c r="J9" s="0">
-        <v>1.7962106874955048</v>
+        <v>0.82890082414078936</v>
       </c>
       <c r="K9" s="0">
-        <v>-1.1486944163902155</v>
+        <v>-1.4418951033126082</v>
       </c>
       <c r="L9" s="0">
-        <v>3.0093845202384681</v>
+        <v>0.45801204623069669</v>
       </c>
       <c r="M9" s="0">
-        <v>0.90241726601622963</v>
+        <v>0.95965597855407603</v>
       </c>
       <c r="N9" s="0">
-        <v>1.739282677935619</v>
+        <v>0.67145936063587441</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.47098761967525243</v>
+        <v>-0.50181254831309619</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.34225660055929197</v>
+        <v>-1.1397485656923887</v>
       </c>
       <c r="Q9" s="0">
-        <v>-4.0831292058468014</v>
+        <v>-1.6869326102730207</v>
       </c>
       <c r="R9" s="0">
-        <v>-0.011651923740797192</v>
+        <v>-0.011616726751034425</v>
       </c>
       <c r="S9" s="0" t="s">
         <v>25</v>
@@ -1266,25 +1266,25 @@
   <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.453125" customWidth="true"/>
-    <col min="2" max="2" width="15.453125" customWidth="true"/>
-    <col min="3" max="3" width="12.453125" customWidth="true"/>
-    <col min="4" max="4" width="13.453125" customWidth="true"/>
-    <col min="5" max="5" width="15.453125" customWidth="true"/>
-    <col min="6" max="6" width="13.453125" customWidth="true"/>
-    <col min="7" max="7" width="13.453125" customWidth="true"/>
-    <col min="8" max="8" width="12.453125" customWidth="true"/>
-    <col min="9" max="9" width="12.453125" customWidth="true"/>
-    <col min="10" max="10" width="12.453125" customWidth="true"/>
-    <col min="11" max="11" width="12.453125" customWidth="true"/>
-    <col min="12" max="12" width="15.453125" customWidth="true"/>
-    <col min="13" max="13" width="14.453125" customWidth="true"/>
-    <col min="14" max="14" width="15.453125" customWidth="true"/>
-    <col min="15" max="15" width="15.08984375" customWidth="true"/>
-    <col min="16" max="16" width="13.453125" customWidth="true"/>
-    <col min="17" max="17" width="15.08984375" customWidth="true"/>
-    <col min="18" max="18" width="12.453125" customWidth="true"/>
-    <col min="19" max="19" width="3.54296875" customWidth="true"/>
+    <col min="1" max="1" width="13.5546875" customWidth="true"/>
+    <col min="2" max="2" width="15.21875" customWidth="true"/>
+    <col min="3" max="3" width="14.5546875" customWidth="true"/>
+    <col min="4" max="4" width="13.5546875" customWidth="true"/>
+    <col min="5" max="5" width="15.5546875" customWidth="true"/>
+    <col min="6" max="6" width="15.21875" customWidth="true"/>
+    <col min="7" max="7" width="13.5546875" customWidth="true"/>
+    <col min="8" max="8" width="13.5546875" customWidth="true"/>
+    <col min="9" max="9" width="14.5546875" customWidth="true"/>
+    <col min="10" max="10" width="12.5546875" customWidth="true"/>
+    <col min="11" max="11" width="13.5546875" customWidth="true"/>
+    <col min="12" max="12" width="15.21875" customWidth="true"/>
+    <col min="13" max="13" width="12.5546875" customWidth="true"/>
+    <col min="14" max="14" width="15.21875" customWidth="true"/>
+    <col min="15" max="15" width="15.5546875" customWidth="true"/>
+    <col min="16" max="16" width="13.5546875" customWidth="true"/>
+    <col min="17" max="17" width="13.5546875" customWidth="true"/>
+    <col min="18" max="18" width="13.5546875" customWidth="true"/>
+    <col min="19" max="19" width="3.6640625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1348,58 +1348,58 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>1.8227705432298154</v>
+        <v>0.17424539896860647</v>
       </c>
       <c r="B2" s="0">
-        <v>0.038756456576420045</v>
+        <v>0.58611892416998179</v>
       </c>
       <c r="C2" s="0">
-        <v>1.4151178017696515</v>
+        <v>0.13262145218312971</v>
       </c>
       <c r="D2" s="0">
-        <v>0.01383683638525938</v>
+        <v>0.028326916491131882</v>
       </c>
       <c r="E2" s="0">
-        <v>1.9913076119083626</v>
+        <v>0.091060249272054694</v>
       </c>
       <c r="F2" s="0">
-        <v>1.0043536878421953</v>
+        <v>0.95775994715690638</v>
       </c>
       <c r="G2" s="0">
-        <v>1.2503700816979722</v>
+        <v>0.37995697364586611</v>
       </c>
       <c r="H2" s="0">
-        <v>1.0616330252580219</v>
+        <v>0.87929302446418722</v>
       </c>
       <c r="I2" s="0">
-        <v>0.78609911012040501</v>
+        <v>0.79692989262787595</v>
       </c>
       <c r="J2" s="0">
-        <v>1.2446329398671865</v>
+        <v>0.76096116828185545</v>
       </c>
       <c r="K2" s="0">
-        <v>0.88792901076734221</v>
+        <v>0.8781928851075409</v>
       </c>
       <c r="L2" s="0">
-        <v>1.8491357429737718</v>
+        <v>0.33881939243312342</v>
       </c>
       <c r="M2" s="0">
-        <v>0.25040579204734348</v>
+        <v>0.6749477527725507</v>
       </c>
       <c r="N2" s="0">
-        <v>1.3520193795877587</v>
+        <v>0.47486182925134912</v>
       </c>
       <c r="O2" s="0">
-        <v>0.79235604424070427</v>
+        <v>0.6795238580974422</v>
       </c>
       <c r="P2" s="0">
-        <v>1.4458963958727664</v>
+        <v>0.14264649887505276</v>
       </c>
       <c r="Q2" s="0">
-        <v>1.8002225422548304</v>
+        <v>0.64046572083401887</v>
       </c>
       <c r="R2" s="0">
-        <v>1.93031931128462</v>
+        <v>0.19623493511992352</v>
       </c>
       <c r="S2" s="0" t="s">
         <v>19</v>
@@ -1407,58 +1407,58 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>1.040473508635412</v>
+        <v>0.886901709871602</v>
       </c>
       <c r="B3" s="0">
-        <v>0.00785955658057832</v>
+        <v>0.31835229998023318</v>
       </c>
       <c r="C3" s="0">
-        <v>0.44702906346044136</v>
+        <v>0.42789698110596608</v>
       </c>
       <c r="D3" s="0">
-        <v>0.28569339920267711</v>
+        <v>0.55397755989375164</v>
       </c>
       <c r="E3" s="0">
-        <v>7.3988823247616219e-23</v>
+        <v>0.062278459525710671</v>
       </c>
       <c r="F3" s="0">
-        <v>0.61223831066196066</v>
+        <v>0.6103767500067564</v>
       </c>
       <c r="G3" s="0">
-        <v>0.49831676389362867</v>
+        <v>0.048366506582685175</v>
       </c>
       <c r="H3" s="0">
-        <v>0.87166473032789382</v>
+        <v>0.76218260352971501</v>
       </c>
       <c r="I3" s="0">
-        <v>0.95469158349013961</v>
+        <v>0.76273630684783311</v>
       </c>
       <c r="J3" s="0">
-        <v>1.1783986807356097</v>
+        <v>0.54030891919309976</v>
       </c>
       <c r="K3" s="0">
-        <v>1.1689266942354326</v>
+        <v>0.7421085751556048</v>
       </c>
       <c r="L3" s="0">
-        <v>1.9480705351894139</v>
+        <v>0.62365254614413923</v>
       </c>
       <c r="M3" s="0">
-        <v>0.0072856607327563211</v>
+        <v>0.53696698487337446</v>
       </c>
       <c r="N3" s="0">
-        <v>1.7369537367399757</v>
+        <v>0.67402753955769001</v>
       </c>
       <c r="O3" s="0">
-        <v>1.9999747390761877</v>
+        <v>0.47716455496960575</v>
       </c>
       <c r="P3" s="0">
-        <v>1.0817361890509702</v>
+        <v>0.78555153910676145</v>
       </c>
       <c r="Q3" s="0">
-        <v>1.9064229834088966</v>
+        <v>0.55926249691622321</v>
       </c>
       <c r="R3" s="0">
-        <v>0.52243317502701392</v>
+        <v>0.011973444139461465</v>
       </c>
       <c r="S3" s="0" t="s">
         <v>20</v>
@@ -1466,58 +1466,58 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>1.5214341099593396</v>
+        <v>0.52058147956890744</v>
       </c>
       <c r="B4" s="0">
-        <v>0.41668226725544888</v>
+        <v>0.84514684371088467</v>
       </c>
       <c r="C4" s="0">
-        <v>0.9122472153168304</v>
+        <v>0.90204092483012466</v>
       </c>
       <c r="D4" s="0">
-        <v>1.5531363157372735</v>
+        <v>0.5200899262575186</v>
       </c>
       <c r="E4" s="0">
-        <v>1.3443700244601053</v>
+        <v>0.83973712802433376</v>
       </c>
       <c r="F4" s="0">
-        <v>0.85229131032667771</v>
+        <v>0.80244081740204909</v>
       </c>
       <c r="G4" s="0">
-        <v>0.96633981281415382</v>
+        <v>0.84573010720084774</v>
       </c>
       <c r="H4" s="0">
-        <v>1.0580258676680197</v>
+        <v>0.38480196961828317</v>
       </c>
       <c r="I4" s="0">
-        <v>0.8634613697505743</v>
+        <v>0.60963320343475202</v>
       </c>
       <c r="J4" s="0">
-        <v>1.6639443979873825</v>
+        <v>0.39761285005827285</v>
       </c>
       <c r="K4" s="0">
-        <v>0.64011937439673461</v>
+        <v>0.64013964893200637</v>
       </c>
       <c r="L4" s="0">
-        <v>0.34293808366280676</v>
+        <v>0.7989194181948589</v>
       </c>
       <c r="M4" s="0">
-        <v>1.7617941027338358</v>
+        <v>0.68214432387318236</v>
       </c>
       <c r="N4" s="0">
-        <v>0.98129863327903777</v>
+        <v>0.97920354262660248</v>
       </c>
       <c r="O4" s="0">
-        <v>4.8387251836241434e-06</v>
+        <v>0.29963328693668878</v>
       </c>
       <c r="P4" s="0">
-        <v>0.97607496742268363</v>
+        <v>0.9006408924936965</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.95966264901712095</v>
+        <v>0.91095995027311738</v>
       </c>
       <c r="R4" s="0">
-        <v>0.97721714133776971</v>
+        <v>0.94935289235353582</v>
       </c>
       <c r="S4" s="0" t="s">
         <v>18</v>
@@ -1525,58 +1525,58 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>1.9928952878814001</v>
+        <v>0.019462028574344675</v>
       </c>
       <c r="B5" s="0">
-        <v>0.00011857441537150456</v>
+        <v>4.2090764869896806e-07</v>
       </c>
       <c r="C5" s="0">
-        <v>0.38622345090618859</v>
+        <v>0.0078812373821294714</v>
       </c>
       <c r="D5" s="0">
-        <v>0.20276280919234047</v>
+        <v>0.12725333264259153</v>
       </c>
       <c r="E5" s="0">
-        <v>0.00044061025340264167</v>
+        <v>0.5374380346332982</v>
       </c>
       <c r="F5" s="0">
-        <v>0.071491802632532964</v>
+        <v>0.13059954677827645</v>
       </c>
       <c r="G5" s="0">
-        <v>0.034369283575814168</v>
+        <v>0.019762888231217232</v>
       </c>
       <c r="H5" s="0">
-        <v>1.9481460506838901</v>
+        <v>0.016491548905758376</v>
       </c>
       <c r="I5" s="0">
-        <v>0.36561553297406857</v>
+        <v>0.0047846963580945538</v>
       </c>
       <c r="J5" s="0">
-        <v>0.48179198846599414</v>
+        <v>0.55524229037137063</v>
       </c>
       <c r="K5" s="0">
-        <v>0.86304457910944465</v>
+        <v>0.33459041664213762</v>
       </c>
       <c r="L5" s="0">
-        <v>0.0093538632741682805</v>
+        <v>0.05095672161711369</v>
       </c>
       <c r="M5" s="0">
-        <v>1.993740695384681</v>
+        <v>0.17400143682365521</v>
       </c>
       <c r="N5" s="0">
-        <v>0.00043096525552696933</v>
+        <v>0.13121787765025283</v>
       </c>
       <c r="O5" s="0">
-        <v>3.0898796501580874e-51</v>
+        <v>0.00049484782454251367</v>
       </c>
       <c r="P5" s="0">
-        <v>0.29681727739133823</v>
+        <v>0.29839263702603913</v>
       </c>
       <c r="Q5" s="0">
-        <v>1.0899980931208402e-16</v>
+        <v>0.028210997148593653</v>
       </c>
       <c r="R5" s="0">
-        <v>0.68064425265514994</v>
+        <v>0.32991890740817775</v>
       </c>
       <c r="S5" s="0" t="s">
         <v>21</v>
@@ -1584,58 +1584,58 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.88239588965368765</v>
+        <v>0.41487771883854319</v>
       </c>
       <c r="B6" s="0">
-        <v>1.3921134223405904</v>
+        <v>0.69939123087922961</v>
       </c>
       <c r="C6" s="0">
-        <v>1.6162681925605407</v>
+        <v>0.38118965695054763</v>
       </c>
       <c r="D6" s="0">
-        <v>1.600045693350153</v>
+        <v>0.51274239841393388</v>
       </c>
       <c r="E6" s="0">
-        <v>2</v>
+        <v>0.0005951304594481845</v>
       </c>
       <c r="F6" s="0">
-        <v>1.8309320014183437</v>
+        <v>0.079465412814596515</v>
       </c>
       <c r="G6" s="0">
-        <v>1.120001091319164</v>
+        <v>0.62126187126036114</v>
       </c>
       <c r="H6" s="0">
-        <v>0.40904532991958509</v>
+        <v>0.17277162982806837</v>
       </c>
       <c r="I6" s="0">
-        <v>1.1828358164773232</v>
+        <v>0.25166494463436295</v>
       </c>
       <c r="J6" s="0">
-        <v>0.83856247491119729</v>
+        <v>0.27676837584889913</v>
       </c>
       <c r="K6" s="0">
-        <v>1.0902215023045108</v>
+        <v>0.72265888327082528</v>
       </c>
       <c r="L6" s="0">
-        <v>1.881412732691456</v>
+        <v>0.70501139263793333</v>
       </c>
       <c r="M6" s="0">
-        <v>1.2419424926285316</v>
+        <v>0.92185312156938426</v>
       </c>
       <c r="N6" s="0">
-        <v>0.92180426363150569</v>
+        <v>0.96479698907482048</v>
       </c>
       <c r="O6" s="0">
-        <v>1.3791940891237624</v>
+        <v>0.91849403219743553</v>
       </c>
       <c r="P6" s="0">
-        <v>1.4146832975924226</v>
+        <v>0.10847344091284117</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.34539461080146583</v>
+        <v>0.77233440652109764</v>
       </c>
       <c r="R6" s="0">
-        <v>0.99924712376170166</v>
+        <v>0.99719736851641427</v>
       </c>
       <c r="S6" s="0" t="s">
         <v>22</v>
@@ -1643,58 +1643,58 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>1.727214371739741</v>
+        <v>0.53005677500987281</v>
       </c>
       <c r="B7" s="0">
-        <v>0.11091630570508559</v>
+        <v>0.2001754085898203</v>
       </c>
       <c r="C7" s="0">
-        <v>1.3670512399990245</v>
+        <v>0.64693889053441112</v>
       </c>
       <c r="D7" s="0">
-        <v>0.98148654355797882</v>
+        <v>0.91948423298496418</v>
       </c>
       <c r="E7" s="0">
-        <v>0.00021633973456282904</v>
+        <v>0.053657417582337663</v>
       </c>
       <c r="F7" s="0">
-        <v>0.021159629734328261</v>
+        <v>4.5233640077386024e-05</v>
       </c>
       <c r="G7" s="0">
-        <v>0.73715622679574788</v>
+        <v>0.67856674738941825</v>
       </c>
       <c r="H7" s="0">
-        <v>1.8672609874365214</v>
+        <v>0.12116607948765246</v>
       </c>
       <c r="I7" s="0">
-        <v>0.40689595061416561</v>
+        <v>0.32385072930167846</v>
       </c>
       <c r="J7" s="0">
-        <v>1.9745232488818019</v>
+        <v>0.21226516284098529</v>
       </c>
       <c r="K7" s="0">
-        <v>0.52690124664078475</v>
+        <v>0.036168236929611845</v>
       </c>
       <c r="L7" s="0">
-        <v>1.6120088004144893</v>
+        <v>0.84222190874687075</v>
       </c>
       <c r="M7" s="0">
-        <v>1.3427797833710451</v>
+        <v>0.42881460135070704</v>
       </c>
       <c r="N7" s="0">
-        <v>0.86498514733476362</v>
+        <v>0.83150953820899276</v>
       </c>
       <c r="O7" s="0">
-        <v>0.0520476443203911</v>
+        <v>0.56595973421731716</v>
       </c>
       <c r="P7" s="0">
-        <v>0.061910545765048536</v>
+        <v>0.037718937016588489</v>
       </c>
       <c r="Q7" s="0">
-        <v>2.2424025862999889e-19</v>
+        <v>0.040974723501322211</v>
       </c>
       <c r="R7" s="0">
-        <v>1.0566680645793451</v>
+        <v>0.94948688257620539</v>
       </c>
       <c r="S7" s="0" t="s">
         <v>23</v>
@@ -1702,58 +1702,58 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>1.8608963752933669</v>
+        <v>0.25748541430722049</v>
       </c>
       <c r="B8" s="0">
-        <v>0.00024736126519364079</v>
+        <v>5.5559652631706548e-06</v>
       </c>
       <c r="C8" s="0">
-        <v>0.92663340588961862</v>
+        <v>0.57323259436292851</v>
       </c>
       <c r="D8" s="0">
-        <v>1.0358697143982914</v>
+        <v>0.91280637931162834</v>
       </c>
       <c r="E8" s="0">
-        <v>7.2243045854077635e-05</v>
+        <v>0.4981891964041768</v>
       </c>
       <c r="F8" s="0">
-        <v>0.43759284600649284</v>
+        <v>0.36171464857666336</v>
       </c>
       <c r="G8" s="0">
-        <v>0.6112395147838442</v>
+        <v>0.48986280794228931</v>
       </c>
       <c r="H8" s="0">
-        <v>1.5354494001406676</v>
+        <v>0.25008895294055411</v>
       </c>
       <c r="I8" s="0">
-        <v>0.68799728038735453</v>
+        <v>0.15793289105404296</v>
       </c>
       <c r="J8" s="0">
-        <v>0.29879432213745505</v>
+        <v>0.44096581603032248</v>
       </c>
       <c r="K8" s="0">
-        <v>0.89198601159399715</v>
+        <v>0.47695022691180322</v>
       </c>
       <c r="L8" s="0">
-        <v>0.00051804290824150026</v>
+        <v>6.971969171953545e-07</v>
       </c>
       <c r="M8" s="0">
-        <v>1.5578187225088092</v>
+        <v>0.44329204583588366</v>
       </c>
       <c r="N8" s="0">
-        <v>2.5139998568940173e-18</v>
+        <v>5.0879489448010006e-05</v>
       </c>
       <c r="O8" s="0">
-        <v>1.2761312844158012e-34</v>
+        <v>0.0011196711459491747</v>
       </c>
       <c r="P8" s="0">
-        <v>0.76804564233921002</v>
+        <v>0.72420045903393082</v>
       </c>
       <c r="Q8" s="0">
-        <v>5.4309102481510046e-14</v>
+        <v>0.014164522207552389</v>
       </c>
       <c r="R8" s="0">
-        <v>1.124250532194027</v>
+        <v>0.67948458299815206</v>
       </c>
       <c r="S8" s="0" t="s">
         <v>24</v>
@@ -1761,58 +1761,58 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.8976221248761006</v>
+        <v>0.95116997822683969</v>
       </c>
       <c r="B9" s="0">
-        <v>1.4172670093692532</v>
+        <v>0.86837140314677752</v>
       </c>
       <c r="C9" s="0">
-        <v>1.7202076316031341</v>
+        <v>0.49259388469991639</v>
       </c>
       <c r="D9" s="0">
-        <v>1.1175488774539908</v>
+        <v>0.70119732445725402</v>
       </c>
       <c r="E9" s="0">
-        <v>1.9999999999621332</v>
+        <v>0.25270970200061538</v>
       </c>
       <c r="F9" s="0">
-        <v>1.1692751902746297</v>
+        <v>0.16070103645395395</v>
       </c>
       <c r="G9" s="0">
-        <v>1.0555472526612413</v>
+        <v>0.79214342225649259</v>
       </c>
       <c r="H9" s="0">
-        <v>0.49497465375342353</v>
+        <v>0.12879109981098869</v>
       </c>
       <c r="I9" s="0">
-        <v>1.2774518083666349</v>
+        <v>0.63645423521065103</v>
       </c>
       <c r="J9" s="0">
-        <v>0.075041587315714906</v>
+        <v>0.40884835627210581</v>
       </c>
       <c r="K9" s="0">
-        <v>1.7469749906970926</v>
+        <v>0.15200337836810196</v>
       </c>
       <c r="L9" s="0">
-        <v>0.0032065975079633912</v>
+        <v>0.64779329128187046</v>
       </c>
       <c r="M9" s="0">
-        <v>0.36868932112604069</v>
+        <v>0.33920735869538388</v>
       </c>
       <c r="N9" s="0">
-        <v>0.084615088045464443</v>
+        <v>0.50325151965267545</v>
       </c>
       <c r="O9" s="0">
-        <v>1.3614734625851284</v>
+        <v>0.61674239380174689</v>
       </c>
       <c r="P9" s="0">
-        <v>1.2672281577347078</v>
+        <v>0.25671902075464315</v>
       </c>
       <c r="Q9" s="0">
-        <v>1.9999183800414442</v>
+        <v>0.094280830719319031</v>
       </c>
       <c r="R9" s="0">
-        <v>1.0092768346466787</v>
+        <v>0.99075118663341455</v>
       </c>
       <c r="S9" s="0" t="s">
         <v>25</v>
@@ -1827,23 +1827,23 @@
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.08984375" customWidth="true"/>
-    <col min="2" max="2" width="5.1796875" customWidth="true"/>
-    <col min="3" max="3" width="4.36328125" customWidth="true"/>
-    <col min="4" max="4" width="4.08984375" customWidth="true"/>
-    <col min="5" max="5" width="3.81640625" customWidth="true"/>
-    <col min="6" max="6" width="10.08984375" customWidth="true"/>
-    <col min="7" max="7" width="5.81640625" customWidth="true"/>
-    <col min="8" max="8" width="7.36328125" customWidth="true"/>
-    <col min="9" max="9" width="3.453125" customWidth="true"/>
-    <col min="10" max="10" width="6.1796875" customWidth="true"/>
-    <col min="11" max="11" width="4.453125" customWidth="true"/>
-    <col min="12" max="12" width="6.08984375" customWidth="true"/>
-    <col min="13" max="13" width="5.7265625" customWidth="true"/>
-    <col min="14" max="14" width="13.453125" customWidth="true"/>
-    <col min="15" max="15" width="4.90625" customWidth="true"/>
-    <col min="16" max="16" width="4" customWidth="true"/>
-    <col min="17" max="17" width="4.81640625" customWidth="true"/>
+    <col min="1" max="1" width="5.109375" customWidth="true"/>
+    <col min="2" max="2" width="5.33203125" customWidth="true"/>
+    <col min="3" max="3" width="4.44140625" customWidth="true"/>
+    <col min="4" max="4" width="4.21875" customWidth="true"/>
+    <col min="5" max="5" width="3.88671875" customWidth="true"/>
+    <col min="6" max="6" width="10" customWidth="true"/>
+    <col min="7" max="7" width="5.88671875" customWidth="true"/>
+    <col min="8" max="8" width="7.44140625" customWidth="true"/>
+    <col min="9" max="9" width="3.44140625" customWidth="true"/>
+    <col min="10" max="10" width="6.109375" customWidth="true"/>
+    <col min="11" max="11" width="4.5546875" customWidth="true"/>
+    <col min="12" max="12" width="6" customWidth="true"/>
+    <col min="13" max="13" width="5.77734375" customWidth="true"/>
+    <col min="14" max="14" width="13.33203125" customWidth="true"/>
+    <col min="15" max="15" width="5" customWidth="true"/>
+    <col min="16" max="16" width="4.109375" customWidth="true"/>
+    <col min="17" max="17" width="4.88671875" customWidth="true"/>
     <col min="18" max="18" width="5" customWidth="true"/>
   </cols>
   <sheetData>
@@ -1968,23 +1968,23 @@
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.08984375" customWidth="true"/>
-    <col min="2" max="2" width="5.1796875" customWidth="true"/>
-    <col min="3" max="3" width="4.36328125" customWidth="true"/>
-    <col min="4" max="4" width="4.08984375" customWidth="true"/>
-    <col min="5" max="5" width="3.81640625" customWidth="true"/>
-    <col min="6" max="6" width="10.08984375" customWidth="true"/>
-    <col min="7" max="7" width="5.81640625" customWidth="true"/>
-    <col min="8" max="8" width="7.36328125" customWidth="true"/>
-    <col min="9" max="9" width="3.453125" customWidth="true"/>
-    <col min="10" max="10" width="6.1796875" customWidth="true"/>
-    <col min="11" max="11" width="4.453125" customWidth="true"/>
-    <col min="12" max="12" width="6.08984375" customWidth="true"/>
-    <col min="13" max="13" width="5.7265625" customWidth="true"/>
-    <col min="14" max="14" width="13.453125" customWidth="true"/>
-    <col min="15" max="15" width="4.90625" customWidth="true"/>
-    <col min="16" max="16" width="4" customWidth="true"/>
-    <col min="17" max="17" width="4.81640625" customWidth="true"/>
+    <col min="1" max="1" width="5.109375" customWidth="true"/>
+    <col min="2" max="2" width="5.33203125" customWidth="true"/>
+    <col min="3" max="3" width="4.44140625" customWidth="true"/>
+    <col min="4" max="4" width="4.21875" customWidth="true"/>
+    <col min="5" max="5" width="3.88671875" customWidth="true"/>
+    <col min="6" max="6" width="10" customWidth="true"/>
+    <col min="7" max="7" width="5.88671875" customWidth="true"/>
+    <col min="8" max="8" width="7.44140625" customWidth="true"/>
+    <col min="9" max="9" width="3.44140625" customWidth="true"/>
+    <col min="10" max="10" width="6.109375" customWidth="true"/>
+    <col min="11" max="11" width="4.5546875" customWidth="true"/>
+    <col min="12" max="12" width="6" customWidth="true"/>
+    <col min="13" max="13" width="5.77734375" customWidth="true"/>
+    <col min="14" max="14" width="13.33203125" customWidth="true"/>
+    <col min="15" max="15" width="5" customWidth="true"/>
+    <col min="16" max="16" width="4.109375" customWidth="true"/>
+    <col min="17" max="17" width="4.88671875" customWidth="true"/>
     <col min="18" max="18" width="5" customWidth="true"/>
   </cols>
   <sheetData>
@@ -2046,58 +2046,58 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>-1.8439760519468145</v>
+        <v>-0.58239101943845983</v>
       </c>
       <c r="B2" s="0">
-        <v>4.2943052448172727</v>
+        <v>3.7749046826235304</v>
       </c>
       <c r="C2" s="0">
-        <v>0.22028741019960832</v>
+        <v>0.062628641379461184</v>
       </c>
       <c r="D2" s="0">
-        <v>0.90470838680036814</v>
+        <v>0.24534884706479782</v>
       </c>
       <c r="E2" s="0">
-        <v>-0.49632858597097818</v>
+        <v>-0.85916888401086744</v>
       </c>
       <c r="F2" s="0">
-        <v>1.432517942687745</v>
+        <v>0.25680877553843934</v>
       </c>
       <c r="G2" s="0">
-        <v>1.3701013659992789</v>
+        <v>0.32833470968534873</v>
       </c>
       <c r="H2" s="0">
-        <v>-1.0120212219722082</v>
+        <v>-0.1510666338074203</v>
       </c>
       <c r="I2" s="0">
-        <v>1.613406605740954</v>
+        <v>0.36787595978518317</v>
       </c>
       <c r="J2" s="0">
-        <v>0.090007634717859622</v>
+        <v>0.029112977915506936</v>
       </c>
       <c r="K2" s="0">
-        <v>0.78262757001668526</v>
+        <v>0.16407470342496755</v>
       </c>
       <c r="L2" s="0">
-        <v>2.0109612140418012</v>
+        <v>2.3629475723954676</v>
       </c>
       <c r="M2" s="0">
-        <v>-0.49090222916354176</v>
+        <v>-0.32242575916981042</v>
       </c>
       <c r="N2" s="0">
-        <v>1.8891571459184227</v>
+        <v>1.3227298968730896</v>
       </c>
       <c r="O2" s="0">
-        <v>2.6032123700114243</v>
+        <v>2.8615754767794663</v>
       </c>
       <c r="P2" s="0">
-        <v>-0.30012485573672815</v>
+        <v>-0.078984879773146749</v>
       </c>
       <c r="Q2" s="0">
-        <v>1.5130743434519169</v>
+        <v>1.1809977725997429</v>
       </c>
       <c r="R2" s="0">
-        <v>0.61652988052298552</v>
+        <v>0.18150668753139926</v>
       </c>
     </row>
   </sheetData>
@@ -2109,23 +2109,23 @@
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="5.08984375" customWidth="true"/>
-    <col min="2" max="2" width="5.1796875" customWidth="true"/>
-    <col min="3" max="3" width="4.36328125" customWidth="true"/>
-    <col min="4" max="4" width="4.08984375" customWidth="true"/>
-    <col min="5" max="5" width="3.81640625" customWidth="true"/>
-    <col min="6" max="6" width="10.08984375" customWidth="true"/>
-    <col min="7" max="7" width="5.81640625" customWidth="true"/>
-    <col min="8" max="8" width="7.36328125" customWidth="true"/>
-    <col min="9" max="9" width="3.453125" customWidth="true"/>
-    <col min="10" max="10" width="6.1796875" customWidth="true"/>
-    <col min="11" max="11" width="4.453125" customWidth="true"/>
-    <col min="12" max="12" width="6.08984375" customWidth="true"/>
-    <col min="13" max="13" width="5.7265625" customWidth="true"/>
-    <col min="14" max="14" width="13.453125" customWidth="true"/>
-    <col min="15" max="15" width="4.90625" customWidth="true"/>
-    <col min="16" max="16" width="4" customWidth="true"/>
-    <col min="17" max="17" width="4.81640625" customWidth="true"/>
+    <col min="1" max="1" width="5.109375" customWidth="true"/>
+    <col min="2" max="2" width="5.33203125" customWidth="true"/>
+    <col min="3" max="3" width="4.44140625" customWidth="true"/>
+    <col min="4" max="4" width="4.21875" customWidth="true"/>
+    <col min="5" max="5" width="3.88671875" customWidth="true"/>
+    <col min="6" max="6" width="10" customWidth="true"/>
+    <col min="7" max="7" width="5.88671875" customWidth="true"/>
+    <col min="8" max="8" width="7.44140625" customWidth="true"/>
+    <col min="9" max="9" width="3.44140625" customWidth="true"/>
+    <col min="10" max="10" width="6.109375" customWidth="true"/>
+    <col min="11" max="11" width="4.5546875" customWidth="true"/>
+    <col min="12" max="12" width="6" customWidth="true"/>
+    <col min="13" max="13" width="5.77734375" customWidth="true"/>
+    <col min="14" max="14" width="13.33203125" customWidth="true"/>
+    <col min="15" max="15" width="5" customWidth="true"/>
+    <col min="16" max="16" width="4.109375" customWidth="true"/>
+    <col min="17" max="17" width="4.88671875" customWidth="true"/>
     <col min="18" max="18" width="5" customWidth="true"/>
   </cols>
   <sheetData>
@@ -2187,58 +2187,58 @@
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.067716734419761615</v>
+        <v>0.56142397878407802</v>
       </c>
       <c r="B2" s="0">
-        <v>3.6364427484188462e-05</v>
+        <v>0.00025297873958478979</v>
       </c>
       <c r="C2" s="0">
-        <v>0.82603124407943929</v>
+        <v>0.95016908904587571</v>
       </c>
       <c r="D2" s="0">
-        <v>0.36747905424529737</v>
+        <v>0.8066161688502671</v>
       </c>
       <c r="E2" s="0">
-        <v>0.62059377660473281</v>
+        <v>0.39200423185822342</v>
       </c>
       <c r="F2" s="0">
-        <v>0.15466206445895891</v>
+        <v>0.79777744854786248</v>
       </c>
       <c r="G2" s="0">
-        <v>0.17327864222082246</v>
+        <v>0.74324549035218368</v>
       </c>
       <c r="H2" s="0">
-        <v>0.31361622890073315</v>
+        <v>0.88018330666059097</v>
       </c>
       <c r="I2" s="0">
-        <v>0.10935019506845867</v>
+        <v>0.71363040184863058</v>
       </c>
       <c r="J2" s="0">
-        <v>0.92843505074868826</v>
+        <v>0.97682408685981992</v>
       </c>
       <c r="K2" s="0">
-        <v>0.43542700779160215</v>
+        <v>0.86995544160730376</v>
       </c>
       <c r="L2" s="0">
-        <v>0.046628538648517792</v>
+        <v>0.019779907274580066</v>
       </c>
       <c r="M2" s="0">
-        <v>0.62441510219884444</v>
+        <v>0.74770560467639014</v>
       </c>
       <c r="N2" s="0">
-        <v>0.061346202652740073</v>
+        <v>0.18850479273870091</v>
       </c>
       <c r="O2" s="0">
-        <v>0.010431030538295707</v>
+        <v>0.004995115363201845</v>
       </c>
       <c r="P2" s="0">
-        <v>0.76461450780223295</v>
+        <v>0.93717958117254985</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.13295737443027555</v>
+        <v>0.23999878330847502</v>
       </c>
       <c r="R2" s="0">
-        <v>0.53874262881807899</v>
+        <v>0.85628395700613702</v>
       </c>
     </row>
   </sheetData>
